--- a/reports/devops-jobs-israel-2026-W31.xlsx
+++ b/reports/devops-jobs-israel-2026-W31.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27T10:05:00</t>
+    <t xml:space="preserve">2026-07-28T08:47:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6%</t>
+    <t xml:space="preserve">3.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -294,6 +294,21 @@
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, CI/CD, Linux, Python, Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
   </si>
   <si>
@@ -474,6 +489,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
   </si>
   <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gotfriends</t>
   </si>
   <si>
@@ -513,6 +537,174 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer | Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-haifa-at-matchpointit-4443246295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magma Devs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-magma-devs-4445644245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36998)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445622695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4445930896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wiz</t>
   </si>
   <si>
@@ -522,666 +714,483 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-play-perfect-4412224665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-extreme-4442726484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4440121853</t>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinity Solutions R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-exodigo-4444440128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X-trodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-x-trodes-4441536083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fayrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-fayrix-4443235545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4444286029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmeq, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-kla-4433797118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kms-lighthouse-4444894579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure DevOps / Infrastructure Engineer | Leading company! (5433)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/azure-devops-infrastructure-engineer-leading-company%21-5433-at-ingima-4445906559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magma Devs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-magma-devs-4445644245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps and Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mend.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-and-security-at-mend-io-4444431341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-ai-4440489888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Automic Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-automic-platform-at-youcc-technologies-ltd-4441528264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4440419841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4444432936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-cloud-security-engineer-at-confidential-4442024831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445622695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brooks-Keret CFO as a Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-brooks-keret-cfo-as-a-service-4442337881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4443042028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-controp-precision-technologies-ltd-4424404648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Full Stack Developer - Data Loss Prevention Cloud Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-full-stack-developer-data-loss-prevention-cloud-service-at-check-point-software-4442350779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dialog</t>
   </si>
   <si>
@@ -1218,7 +1227,7 @@
     <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
     <t xml:space="preserve">IOT student tester</t>
@@ -1248,21 +1257,6 @@
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
@@ -1272,6 +1266,45 @@
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
@@ -1284,19 +1317,19 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1448,7 +1481,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -1456,7 +1489,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -1464,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1505,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1099</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10">
@@ -1480,7 +1513,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1544,7 +1577,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -1552,7 +1585,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1571,28 +1604,28 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
@@ -1600,15 +1633,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1627,63 +1660,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>429</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>418</v>
+        <v>340</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B4" s="3">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>335</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>432</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -1691,23 +1724,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="B10" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>199</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
         <v>15</v>
@@ -1715,23 +1748,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B12" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1739,15 +1772,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>425</v>
+        <v>334</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -1775,13 +1808,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
@@ -1789,13 +1822,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1804,88 +1837,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3">
-        <v>37.2</v>
+        <v>38.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.3</v>
+        <v>16.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>17.5</v>
+        <v>16.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1897,7 +1930,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -1969,7 +2002,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -2001,7 +2034,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2033,7 +2066,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -2065,7 +2098,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -2097,7 +2130,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -2129,7 +2162,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -2161,7 +2194,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -2193,7 +2226,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -2225,7 +2258,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -2257,7 +2290,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -2289,7 +2322,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -2321,7 +2354,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -2338,19 +2371,19 @@
         <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -2358,7 +2391,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>86</v>
@@ -2373,27 +2406,27 @@
         <v>38</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>87</v>
@@ -2414,7 +2447,7 @@
         <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="J16" s="3">
         <v>60</v>
@@ -2422,13 +2455,13 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2437,65 +2470,65 @@
         <v>38</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J18" s="3">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>43</v>
@@ -2510,24 +2543,24 @@
         <v>114</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>76</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>43</v>
@@ -2542,134 +2575,136 @@
         <v>119</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="J21" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J22" s="3">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>131</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -2680,17 +2715,15 @@
         <v>139</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
@@ -2698,54 +2731,56 @@
         <v>141</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="J25" s="3">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="J26" s="3">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2755,27 +2790,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2785,27 +2820,27 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2815,27 +2850,27 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2845,27 +2880,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="J30" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2875,27 +2910,27 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="J31" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2911,21 +2946,21 @@
         <v>166</v>
       </c>
       <c r="J32" s="3">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -2935,27 +2970,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="J33" s="3">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -2965,27 +3000,27 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -2995,87 +3030,87 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3085,27 +3120,27 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
@@ -3115,27 +3150,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3145,27 +3180,27 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>43</v>
@@ -3175,13 +3210,13 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>196</v>
+        <v>95</v>
       </c>
       <c r="J41" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3192,17 +3227,15 @@
         <v>198</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>199</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
@@ -3210,7 +3243,7 @@
         <v>200</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3218,75 +3251,75 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>209</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3299,27 +3332,27 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="J45" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>43</v>
@@ -3329,13 +3362,13 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>215</v>
+        <v>46</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3382,7 @@
         <v>218</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
@@ -3362,10 +3395,10 @@
         <v>219</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="J47" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3373,13 +3406,13 @@
         <v>220</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3392,24 +3425,24 @@
         <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>208</v>
+        <v>95</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3419,24 +3452,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3452,21 +3485,21 @@
         <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="J50" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>49</v>
@@ -3482,51 +3515,51 @@
         <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>233</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3539,73 +3572,73 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J53" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="J54" s="3">
-        <v>64</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>244</v>
+        <v>152</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="J55" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -3613,10 +3646,10 @@
         <v>78</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
@@ -3629,60 +3662,60 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J56" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="J57" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3692,24 +3725,24 @@
         <v>253</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="J58" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>43</v>
@@ -3722,21 +3755,21 @@
         <v>257</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="J59" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3752,27 +3785,27 @@
         <v>260</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
@@ -3782,54 +3815,54 @@
         <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>111</v>
+        <v>268</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>117</v>
+        <v>252</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3839,40 +3872,40 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>111</v>
+        <v>271</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>268</v>
+        <v>152</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="J64" s="3">
         <v>6</v>
@@ -3880,91 +3913,89 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>111</v>
+        <v>274</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>116</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="J67" s="3">
         <v>6</v>
@@ -3972,16 +4003,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>116</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>43</v>
@@ -3991,27 +4022,27 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>281</v>
+        <v>180</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4021,27 +4052,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="J69" s="3">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>152</v>
+        <v>279</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4051,10 +4082,10 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4062,16 +4093,16 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4081,27 +4112,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
@@ -4111,27 +4142,27 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="J72" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>155</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>43</v>
@@ -4141,87 +4172,87 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="J73" s="3">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>163</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>302</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="J75" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>163</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>268</v>
+        <v>173</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>43</v>
@@ -4231,27 +4262,27 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="J76" s="3">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4261,17 +4292,257 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>307</v>
+        <v>186</v>
       </c>
       <c r="J77" s="3">
-        <v>35</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J78" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J80" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J84" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J85" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J77"/>
+  <autoFilter ref="A1:J85"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4349,6 +4620,14 @@
     <hyperlink ref="H75" r:id="rId74"/>
     <hyperlink ref="H76" r:id="rId75"/>
     <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4357,7 +4636,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4390,13 +4669,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4404,37 +4683,37 @@
         <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4442,18 +4721,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4461,18 +4740,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4480,18 +4759,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>152</v>
+        <v>218</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4499,18 +4778,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4518,15 +4797,15 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>152</v>
@@ -4537,18 +4816,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>152</v>
+        <v>279</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4556,11 +4835,182 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G19"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4571,6 +5021,15 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4584,15 +5043,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="B2" s="3">
         <v>14</v>
@@ -4600,7 +5059,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3">
         <v>13</v>
@@ -4608,7 +5067,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3">
         <v>13</v>
@@ -4616,23 +5075,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>312</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -4640,7 +5099,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -4648,7 +5107,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -4656,15 +5115,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -4672,7 +5131,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4680,7 +5139,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4688,7 +5147,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -4696,7 +5155,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -4704,7 +5163,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -4726,15 +5185,15 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -4747,15 +5206,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -4763,7 +5222,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -4779,7 +5238,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -4787,7 +5246,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4795,7 +5254,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -4803,7 +5262,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -4811,7 +5270,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -4819,15 +5278,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -4835,7 +5294,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -4843,7 +5302,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -4864,16 +5323,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
@@ -4881,13 +5340,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3">
-        <v>10.9</v>
+        <v>16.8</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -4895,13 +5354,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4909,13 +5368,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4923,13 +5382,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="C5" s="3">
-        <v>8.8</v>
+        <v>9.8</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4937,13 +5396,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>8.8</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4965,7 +5424,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3">
         <v>5.3</v>
@@ -4979,7 +5438,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
         <v>2.9</v>
@@ -4993,7 +5452,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C10" s="3">
         <v>2.4</v>
@@ -5007,7 +5466,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C11" s="3">
         <v>2.4</v>
@@ -5021,7 +5480,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
@@ -5035,7 +5494,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5049,13 +5508,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="C14" s="3">
-        <v>2.0</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5063,10 +5522,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C15" s="3">
-        <v>1.7</v>
+        <v>2.0</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -5077,10 +5536,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C16" s="3">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -5103,18 +5562,18 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5125,10 +5584,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4">
@@ -5139,7 +5598,7 @@
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5158,7 +5617,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
@@ -5166,15 +5625,15 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -5187,7 +5646,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -5195,15 +5654,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5211,9 +5670,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5226,7 +5693,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5238,10 +5705,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5253,10 +5720,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5273,31 +5740,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
@@ -5305,31 +5772,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>208</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -5337,31 +5804,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>347</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
@@ -5369,31 +5836,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
@@ -5401,31 +5868,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>353</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>356</v>
+        <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>180</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -5433,31 +5900,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>210</v>
+        <v>377</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>358</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="F7" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>361</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -5465,31 +5932,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>363</v>
+        <v>152</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="F8" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -5497,31 +5964,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>368</v>
+        <v>247</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>369</v>
+        <v>152</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
@@ -5529,31 +5996,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>379</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -5561,31 +6028,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -5593,31 +6060,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>381</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F12" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>386</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -5625,31 +6092,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>152</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F13" s="3">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>208</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -5657,31 +6124,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="F14" s="3">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>90</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15">
@@ -5689,31 +6156,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>234</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="F15" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>145</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16">
@@ -5721,31 +6188,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>397</v>
+        <v>127</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>281</v>
+        <v>128</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>254</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -5753,31 +6220,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>400</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>401</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F17" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>403</v>
+        <v>62</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>404</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -5785,31 +6252,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19">
@@ -5817,31 +6284,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>413</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
@@ -5849,31 +6316,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>374</v>
+        <v>422</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>122</v>
+        <v>247</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>84</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21">
@@ -5881,31 +6348,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>58</v>
+        <v>425</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>59</v>
+        <v>393</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>62</v>
+        <v>427</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W31.xlsx
+++ b/reports/devops-jobs-israel-2026-W31.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="439">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28T08:47:35</t>
+    <t xml:space="preserve">2026-07-29T08:52:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6%</t>
+    <t xml:space="preserve">2.4%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -462,762 +462,759 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4443370175</t>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfinityLabs R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-peax-dorcom-4443244980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4444290253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4445930896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logica-IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer | Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-haifa-at-matchpointit-4443246295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (36998)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445622695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4446049070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior ML Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ml-infra-engineer-at-immunai-4445983768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps/IT Enginee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-manager-at-applied-materials-israel-4441537793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Hadarly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-hr-hadarly-4445941974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks-Keret CFO as a Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-brooks-keret-cfo-as-a-service-4443680812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network &amp; Information Security Infrastructure Engineer (37020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-information-security-infrastructure-engineer-37020-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446579191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverbed Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Infrastructure- Lab Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-infrastructure-lab-engineer-at-vast-data-4445154255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML Software &amp; Infrastructure Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-software-infrastructure-engineer-student-position-at-mobileye-4443239639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4443344848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integress, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-integress-inc-4442687060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elbit-systems-israel-4412221373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4443343825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer | Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-haifa-at-matchpointit-4443246295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-riverside-4431928700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magma Devs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-magma-devs-4445644245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445622695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4445930896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443763589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-glow-4443715634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinity Solutions R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-infinity-solutions-r2-4442613436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-exodigo-4444440128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X-trodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-x-trodes-4441536083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-hp-4444407898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-fayrix-4443235545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מהנדס.ת Sys DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9E%D7%94%D7%A0%D7%93%D7%A1-%D7%AA-sys-devops-at-elbit-systems-israel-4412813583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4444286029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmeq, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-kla-4433797118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kms-lighthouse-4444894579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1245,18 +1242,6 @@
     <t xml:space="preserve">2026-06-29</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
@@ -1275,9 +1260,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">QuantHealth</t>
   </si>
   <si>
@@ -1314,22 +1296,19 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1481,7 +1460,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -1489,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1497,7 +1476,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -1505,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1117</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="10">
@@ -1513,7 +1492,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1577,7 +1556,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -1604,44 +1583,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1660,39 +1639,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -1703,20 +1682,20 @@
         <v>335</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -1724,39 +1703,39 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B9" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -1764,7 +1743,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -1772,7 +1751,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -1780,10 +1759,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>436</v>
+        <v>329</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1808,13 +1787,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
@@ -1825,10 +1804,10 @@
         <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>13.8</v>
+        <v>15.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1837,88 +1816,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>38.9</v>
+        <v>34.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.8</v>
+        <v>30.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.4</v>
+        <v>22.7</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1930,7 +1909,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2002,7 +1981,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -2034,7 +2013,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2066,7 +2045,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -2098,7 +2077,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -2130,7 +2109,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -2162,7 +2141,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -2194,7 +2173,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -2226,7 +2205,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -2258,7 +2237,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -2290,7 +2269,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -2322,7 +2301,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -2354,7 +2333,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -2386,7 +2365,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2418,7 +2397,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2450,7 +2429,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -2482,7 +2461,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -2514,7 +2493,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -2546,7 +2525,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -2578,7 +2557,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -2610,7 +2589,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -2642,7 +2621,7 @@
         <v>131</v>
       </c>
       <c r="J22" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -2672,7 +2651,7 @@
         <v>134</v>
       </c>
       <c r="J23" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -2704,7 +2683,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -2734,7 +2713,7 @@
         <v>142</v>
       </c>
       <c r="J25" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2766,7 +2745,7 @@
         <v>77</v>
       </c>
       <c r="J26" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27">
@@ -2780,7 +2759,7 @@
         <v>148</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>43</v>
@@ -2810,7 +2789,7 @@
         <v>152</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2823,10 +2802,10 @@
         <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2834,13 +2813,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2850,13 +2829,13 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J29" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2864,10 +2843,10 @@
         <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
@@ -2880,57 +2859,57 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>43</v>
@@ -2940,18 +2919,18 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>168</v>
@@ -2973,24 +2952,24 @@
         <v>170</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="J33" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3000,10 +2979,10 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -3014,10 +2993,10 @@
         <v>116</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3030,13 +3009,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="J35" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3044,10 +3023,10 @@
         <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>122</v>
@@ -3060,54 +3039,54 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="J37" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>122</v>
@@ -3120,10 +3099,10 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J38" s="3">
         <v>1</v>
@@ -3131,16 +3110,16 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
@@ -3150,27 +3129,27 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3180,10 +3159,10 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J40" s="3">
         <v>1</v>
@@ -3194,13 +3173,13 @@
         <v>116</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>43</v>
@@ -3210,10 +3189,10 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
@@ -3221,16 +3200,16 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>43</v>
@@ -3240,27 +3219,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>43</v>
@@ -3270,86 +3249,84 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>208</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="J44" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>122</v>
@@ -3362,27 +3339,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
@@ -3392,27 +3369,27 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>43</v>
@@ -3422,13 +3399,13 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>95</v>
+        <v>215</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
@@ -3436,13 +3413,13 @@
         <v>116</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>43</v>
@@ -3452,24 +3429,24 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3482,27 +3459,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>116</v>
+        <v>223</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>43</v>
@@ -3512,27 +3489,27 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="J51" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
@@ -3542,87 +3519,87 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="J52" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>158</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="J53" s="3">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>237</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>240</v>
+        <v>53</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -3632,87 +3609,87 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="J55" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="J56" s="3">
-        <v>43</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>95</v>
+        <v>242</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3722,54 +3699,54 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="J59" s="3">
-        <v>69</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3782,24 +3759,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3812,27 +3789,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>263</v>
+        <v>95</v>
       </c>
       <c r="J61" s="3">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3842,27 +3819,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="J62" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>43</v>
@@ -3872,54 +3849,54 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J63" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>150</v>
+        <v>264</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>122</v>
@@ -3932,103 +3909,103 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>277</v>
+        <v>116</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="J66" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>116</v>
+        <v>265</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>281</v>
+        <v>240</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="J68" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4036,13 +4013,13 @@
         <v>116</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>43</v>
@@ -4052,27 +4029,27 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>116</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4082,10 +4059,10 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -4093,16 +4070,16 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4112,27 +4089,27 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>60</v>
+        <v>288</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
@@ -4142,10 +4119,10 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J72" s="3">
         <v>0</v>
@@ -4153,76 +4130,76 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>295</v>
+        <v>162</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>163</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>298</v>
+        <v>165</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="J74" s="3">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>301</v>
+        <v>169</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>302</v>
+        <v>122</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>43</v>
@@ -4232,10 +4209,10 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J75" s="3">
         <v>0</v>
@@ -4243,46 +4220,46 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>173</v>
+        <v>228</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="J76" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>210</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4292,27 +4269,27 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>163</v>
+        <v>287</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>43</v>
@@ -4322,24 +4299,24 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="J78" s="3">
-        <v>70</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>122</v>
@@ -4352,24 +4329,24 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
@@ -4382,40 +4359,42 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="J80" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>317</v>
+        <v>224</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>252</v>
+        <v>122</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F81" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -4423,13 +4402,13 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>122</v>
@@ -4442,57 +4421,57 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>95</v>
+        <v>318</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>179</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4502,47 +4481,17 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>227</v>
+        <v>318</v>
       </c>
       <c r="J84" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J85"/>
+  <autoFilter ref="A1:J84"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4627,7 +4576,6 @@
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
     <hyperlink ref="H84" r:id="rId83"/>
-    <hyperlink ref="H85" r:id="rId84"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4636,7 +4584,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4669,21 +4617,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>148</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
@@ -4691,10 +4639,10 @@
         <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4702,18 +4650,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4721,7 +4669,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -4729,10 +4677,10 @@
         <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4740,18 +4688,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4759,18 +4707,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4778,18 +4726,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4797,18 +4745,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4816,18 +4764,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4835,18 +4783,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>116</v>
+        <v>286</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>287</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4854,18 +4802,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -4873,18 +4821,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -4892,18 +4840,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>301</v>
+        <v>169</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -4911,106 +4859,11 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B15" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>328</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5025,11 +4878,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5043,15 +4891,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B2" s="3">
         <v>14</v>
@@ -5059,7 +4907,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B3" s="3">
         <v>13</v>
@@ -5067,7 +4915,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3">
         <v>13</v>
@@ -5075,7 +4923,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -5083,7 +4931,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
@@ -5091,7 +4939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B7" s="3">
         <v>9</v>
@@ -5099,7 +4947,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -5107,7 +4955,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -5115,7 +4963,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5123,7 +4971,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -5131,7 +4979,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5147,7 +4995,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5155,7 +5003,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5163,7 +5011,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5176,7 +5024,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5185,20 +5033,20 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5206,15 +5054,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5222,7 +5070,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5230,15 +5078,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5246,7 +5094,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5254,7 +5102,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5262,7 +5110,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5270,7 +5118,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5278,7 +5126,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5286,23 +5134,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>240</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>287</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5316,23 +5164,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
@@ -5382,13 +5230,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C5" s="3">
-        <v>9.8</v>
+        <v>8.8</v>
       </c>
       <c r="D5" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5396,13 +5244,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>8.8</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5410,10 +5258,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5424,13 +5272,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="C8" s="3">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5438,13 +5286,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5452,13 +5300,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5466,10 +5314,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="C11" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -5480,7 +5328,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="C12" s="3">
         <v>2.4</v>
@@ -5494,7 +5342,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -5508,7 +5356,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5522,13 +5370,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="C15" s="3">
-        <v>2.0</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5536,13 +5384,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>287</v>
       </c>
       <c r="C16" s="3">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5562,10 +5410,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2">
@@ -5573,7 +5421,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5584,10 +5432,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -5595,10 +5443,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5617,7 +5465,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2">
@@ -5625,7 +5473,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -5638,26 +5486,26 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5673,14 +5521,6 @@
         <v>140</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5693,7 +5533,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5705,10 +5545,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5720,10 +5560,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5740,31 +5580,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
@@ -5772,31 +5612,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>364</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -5804,31 +5644,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>230</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5">
@@ -5836,31 +5676,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>184</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
@@ -5868,31 +5708,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F6" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -5900,31 +5740,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>376</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>377</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F7" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>380</v>
+        <v>45</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -5932,31 +5772,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>385</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -5964,31 +5804,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>247</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F9" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -5996,31 +5836,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>390</v>
+        <v>252</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F10" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>227</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11">
@@ -6028,28 +5868,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F11" s="3">
         <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>90</v>
@@ -6060,31 +5900,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -6092,31 +5932,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="F13" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>84</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14">
@@ -6124,31 +5964,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>407</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -6156,31 +5996,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>234</v>
+        <v>403</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F15" s="3">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16">
@@ -6188,7 +6028,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>127</v>
@@ -6197,19 +6037,19 @@
         <v>128</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>84</v>
@@ -6229,13 +6069,13 @@
         <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F17" s="3">
         <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>24</v>
@@ -6252,31 +6092,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F18" s="3">
         <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>418</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19">
@@ -6284,31 +6124,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F19" s="3">
         <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20">
@@ -6316,31 +6156,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F20" s="3">
         <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21">
@@ -6348,31 +6188,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F21" s="3">
         <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W31.xlsx
+++ b/reports/devops-jobs-israel-2026-W31.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="477">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29T08:52:08</t>
+    <t xml:space="preserve">2026-07-30T08:42:50</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4%</t>
+    <t xml:space="preserve">2.2%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -399,6 +399,21 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
   </si>
   <si>
@@ -462,541 +477,619 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
   </si>
   <si>
-    <t xml:space="preserve">eyesAtop</t>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443876107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eyesatop-4443174554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443132750</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-abra-4446717885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nisha-pro-4444120822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (25323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Engineer - Entry Level Career Path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InfinityLabs R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-entry-level-career-path-at-infinitylabs-r-d-4443775849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-peax-dorcom-4443244980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linnovate Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-position-at-lab42-4445607255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
   </si>
   <si>
     <t xml:space="preserve">Jobgether</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobgether-4444290253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-sela-4445930896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-logica-it-4443283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer | Haifa</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps and Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mend.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-and-security-at-mend-io-4444431341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratacom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualcomm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior ML Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ml-infra-engineer-at-immunai-4445983768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps/IT Enginee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Azure / DevOps)</t>
   </si>
   <si>
     <t xml:space="preserve">MatchPointIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-haifa-at-matchpointit-4443246295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-azure-devops-at-matchpointit-4444557296</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (36998)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-36998-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4445622695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Hadarly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-hr-hadarly-4445941974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-log-on-software-4442343639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Private Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-shavit-software-4444427268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-exodigo-4444440128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobscroller-4444835562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4444119342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375558561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmeq, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-kla-4433797118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communications System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communications-system-engineer-at-iai-israel-aerospace-industries-4443271695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
   </si>
   <si>
     <t xml:space="preserve">KMS Lighthouse</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4446049070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior ML Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ml-infra-engineer-at-immunai-4445983768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps/IT Enginee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-manager-at-applied-materials-israel-4441537793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Hadarly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-hr-hadarly-4445941974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brooks-Keret CFO as a Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-brooks-keret-cfo-as-a-service-4443680812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4441077865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4405133158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network &amp; Information Security Infrastructure Engineer (37020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-information-security-infrastructure-engineer-37020-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446579191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverbed Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-of-devops-at-riverbed-technology-4408088831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Infrastructure DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-infrastructure-devops-engineer-at-armis-4416666118</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kms-lighthouse-4446064508</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1008,21 +1101,18 @@
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
@@ -1059,10 +1149,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1%</t>
+    <t xml:space="preserve">60.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1089,27 +1179,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Infrastructure- Lab Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-infrastructure-lab-engineer-at-vast-data-4445154255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
   </si>
   <si>
@@ -1134,6 +1212,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-systems-engineer-at-nso-group-4443299999</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -1143,16 +1233,76 @@
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-operations-engineer-at-igates-information-gates-ltd-4442889333</t>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar-Ilan University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-bar-ilan-university-4446564670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives Intralogistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
@@ -1161,9 +1311,6 @@
     <t xml:space="preserve">Autobrains Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
   </si>
   <si>
@@ -1185,6 +1332,15 @@
     <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -1194,15 +1350,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
   </si>
   <si>
-    <t xml:space="preserve">ML Software &amp; Infrastructure Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ml-software-infrastructure-engineer-student-position-at-mobileye-4443239639</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -1212,9 +1359,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1227,64 +1371,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantHealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1296,19 +1407,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1460,7 +1574,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1468,7 +1582,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1476,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1598,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1130</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="10">
@@ -1556,7 +1670,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1564,7 +1678,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1583,44 +1697,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1639,95 +1753,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>335</v>
+        <v>462</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>333</v>
+        <v>466</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>429</v>
+        <v>296</v>
       </c>
       <c r="B12" s="3">
         <v>14</v>
@@ -1735,34 +1849,34 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>330</v>
+        <v>467</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1787,13 +1901,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
@@ -1801,13 +1915,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3">
-        <v>15.0</v>
+        <v>12.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1816,88 +1930,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>34.3</v>
+        <v>39.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.5</v>
+        <v>34.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.6</v>
+        <v>19.8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>22.7</v>
+        <v>15.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1909,8 +2023,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1981,7 +2095,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -2013,7 +2127,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2045,7 +2159,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -2077,7 +2191,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -2109,7 +2223,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -2141,7 +2255,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -2173,7 +2287,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -2205,7 +2319,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -2237,7 +2351,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -2269,7 +2383,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -2301,7 +2415,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -2333,7 +2447,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -2365,7 +2479,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2397,7 +2511,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2429,7 +2543,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
@@ -2461,7 +2575,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
@@ -2493,7 +2607,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -2525,7 +2639,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -2557,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -2589,7 +2703,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -2600,7 +2714,7 @@
         <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2609,111 +2723,113 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J22" s="3">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>136</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="J24" s="3">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="J25" s="3">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
@@ -2724,17 +2840,15 @@
         <v>144</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>145</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
@@ -2742,40 +2856,42 @@
         <v>146</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="G27" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
@@ -2783,13 +2899,13 @@
         <v>116</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2799,13 +2915,13 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2816,10 +2932,10 @@
         <v>155</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2829,10 +2945,10 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2846,10 +2962,10 @@
         <v>158</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2859,18 +2975,18 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>161</v>
@@ -2882,7 +2998,7 @@
         <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
@@ -2892,10 +3008,10 @@
         <v>163</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J31" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2903,10 +3019,10 @@
         <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -2922,10 +3038,10 @@
         <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="J32" s="3">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2933,13 +3049,13 @@
         <v>116</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>43</v>
@@ -2949,27 +3065,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="J33" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -2982,7 +3098,7 @@
         <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -2996,10 +3112,10 @@
         <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3009,13 +3125,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3023,13 +3139,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3039,13 +3155,13 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -3053,10 +3169,10 @@
         <v>116</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>122</v>
@@ -3069,27 +3185,27 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3099,48 +3215,48 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="J38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>187</v>
@@ -3165,21 +3281,21 @@
         <v>95</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>43</v>
@@ -3189,27 +3305,27 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>43</v>
@@ -3219,27 +3335,27 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>43</v>
@@ -3249,13 +3365,13 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -3263,13 +3379,13 @@
         <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>43</v>
@@ -3279,13 +3395,13 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="J44" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3293,13 +3409,13 @@
         <v>116</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
@@ -3309,27 +3425,27 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>43</v>
@@ -3339,27 +3455,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="J46" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
@@ -3369,13 +3485,13 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -3383,10 +3499,10 @@
         <v>116</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
@@ -3399,70 +3515,70 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J48" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>116</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>218</v>
+        <v>130</v>
       </c>
       <c r="J49" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J50" s="3">
         <v>22</v>
@@ -3470,13 +3586,13 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>122</v>
@@ -3489,10 +3605,10 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="J51" s="3">
         <v>2</v>
@@ -3500,16 +3616,16 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
@@ -3519,30 +3635,30 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>157</v>
+        <v>229</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3552,144 +3668,146 @@
         <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="J54" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="J56" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J57" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>38</v>
@@ -3699,24 +3817,24 @@
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="J58" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3729,24 +3847,24 @@
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3759,24 +3877,24 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="J60" s="3">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3789,27 +3907,27 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3819,57 +3937,57 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>242</v>
+        <v>179</v>
       </c>
       <c r="J63" s="3">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>43</v>
@@ -3879,24 +3997,24 @@
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="J64" s="3">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>155</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>122</v>
@@ -3909,24 +4027,24 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>270</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -3939,117 +4057,117 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>272</v>
+        <v>153</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J67" s="3">
-        <v>26</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>148</v>
+        <v>280</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>157</v>
+        <v>282</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>116</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>280</v>
+        <v>164</v>
       </c>
       <c r="J69" s="3">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4059,27 +4177,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>116</v>
+        <v>291</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>267</v>
+        <v>174</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4089,10 +4207,10 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="J71" s="3">
         <v>1</v>
@@ -4100,29 +4218,31 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="J72" s="3">
         <v>0</v>
@@ -4130,43 +4250,43 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>290</v>
+        <v>116</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4179,57 +4299,57 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="J74" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>116</v>
+        <v>302</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>53</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4239,114 +4359,116 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="J77" s="3">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>53</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>288</v>
+        <v>162</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="J78" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>309</v>
+        <v>153</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
@@ -4359,56 +4481,54 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="J80" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>312</v>
-      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>157</v>
+        <v>319</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>122</v>
@@ -4421,77 +4541,377 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="J82" s="3">
-        <v>70</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>235</v>
+        <v>326</v>
       </c>
       <c r="J83" s="3">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c r="J84" s="3">
-        <v>70</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J86" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J88" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J89" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J91" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J93" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J84"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4576,6 +4996,16 @@
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
     <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4583,9 +5013,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4617,21 +5047,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
@@ -4639,10 +5069,10 @@
         <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4650,7 +5080,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
@@ -4658,10 +5088,10 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4669,7 +5099,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
@@ -4677,10 +5107,10 @@
         <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4688,7 +5118,7 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6">
@@ -4696,10 +5126,10 @@
         <v>116</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4707,18 +5137,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4726,18 +5156,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4745,18 +5175,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>275</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4764,18 +5194,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4783,18 +5213,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4802,18 +5232,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -4821,18 +5251,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>116</v>
+        <v>312</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -4840,18 +5270,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>311</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -4859,11 +5289,87 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>313</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G18"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4878,6 +5384,10 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4891,39 +5401,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>329</v>
+        <v>242</v>
       </c>
       <c r="B3" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -4931,55 +5441,55 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="B6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>150</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -4987,7 +5497,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>145</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -4995,7 +5505,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5003,7 +5513,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5011,7 +5521,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5024,7 +5534,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5033,7 +5543,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5054,23 +5564,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>287</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5078,7 +5588,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5086,15 +5596,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5102,7 +5612,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5110,7 +5620,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5118,7 +5628,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5126,7 +5636,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5134,7 +5644,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5142,7 +5652,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5164,23 +5674,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5230,7 +5740,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C5" s="3">
         <v>8.8</v>
@@ -5258,13 +5768,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -5272,13 +5782,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>287</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5286,13 +5796,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="C9" s="3">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5300,13 +5810,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>215</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5314,13 +5824,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5328,10 +5838,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C12" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
         <v>2</v>
@@ -5342,13 +5852,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>216</v>
+        <v>127</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5356,7 +5866,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5370,7 +5880,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5384,7 +5894,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5410,10 +5920,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
@@ -5432,10 +5942,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4">
@@ -5443,10 +5953,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -5465,7 +5975,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5473,7 +5983,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -5481,20 +5991,20 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5502,7 +6012,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5510,15 +6020,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>289</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5533,7 +6043,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -5545,10 +6055,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5560,10 +6070,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5580,31 +6090,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -5612,31 +6122,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4">
@@ -5644,31 +6154,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>362</v>
+        <v>393</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>365</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5">
@@ -5676,31 +6186,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
@@ -5717,13 +6227,13 @@
         <v>87</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="F6" s="3">
         <v>92</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>24</v>
@@ -5749,13 +6259,13 @@
         <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="F7" s="3">
         <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
@@ -5772,31 +6282,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>375</v>
+        <v>170</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>95</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -5804,31 +6314,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>165</v>
+        <v>411</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>413</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>383</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -5836,31 +6346,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>252</v>
+        <v>415</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -5868,31 +6378,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>90</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12">
@@ -5900,31 +6410,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>220</v>
+        <v>422</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>148</v>
+        <v>423</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="F12" s="3">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>95</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
@@ -5932,31 +6442,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>426</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>423</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>397</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -5964,31 +6474,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>84</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15">
@@ -5996,31 +6506,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>403</v>
+        <v>235</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16">
@@ -6028,31 +6538,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>378</v>
+        <v>437</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">
@@ -6060,31 +6570,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>428</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>440</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>62</v>
+        <v>442</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
@@ -6092,31 +6602,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>410</v>
+        <v>443</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>211</v>
+        <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>411</v>
+        <v>444</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>222</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19">
@@ -6124,31 +6634,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>154</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -6156,31 +6666,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>257</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21">
@@ -6188,31 +6698,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>388</v>
+        <v>455</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>208</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W31.xlsx
+++ b/reports/devops-jobs-israel-2026-W31.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30T08:42:50</t>
+    <t xml:space="preserve">2026-07-31T09:13:07</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2%</t>
+    <t xml:space="preserve">1.1%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -432,693 +432,696 @@
     <t xml:space="preserve">2026-06-07</t>
   </si>
   <si>
-    <t xml:space="preserve">QA Automation Engineer (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8542303002</t>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445035673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-datateam-4445010424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-abra-4446717885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4445937741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 20705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-20705-at-comblack-4447008409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4443820290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-position-at-lab42-4445607255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tools &amp; Automation Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integra LifeSciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tools-automation-specialist-at-integra-lifesciences-4377406238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratacom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-platform-engineer-at-vidaa-4444520220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-log-on-software-4442343639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps/IT Enginee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4444119342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-snke-4445005467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
   </si>
   <si>
     <t xml:space="preserve">JobScroller</t>
   </si>
   <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-jobscroller-4443876107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-abra-4446717885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nisha Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nisha-pro-4444120822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4442838784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25323-at-yael-group-4441506314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linnovate Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-linnovate-technologies-4441093873</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobscroller-4444835562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Satellite System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsatellite-system-engineer-at-jobsseek-4445198084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Istra Research Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-istra-research-ltd-4445368227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-position-at-lab42-4445607255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-paragon-4429026973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps and Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mend.io</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-and-security-at-mend-io-4444431341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-wiz-4406744533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratacom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-at-mobileye-4416181276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4392358368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer Kfar Netter, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qualcomm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Netter, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kfar-netter-israel-at-qualcomm-4426098218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior ML Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ml-infra-engineer-at-immunai-4445983768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps/IT Enginee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer (Azure / DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-azure-devops-at-matchpointit-4444557296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Hadarly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-devops-engineer-at-hr-hadarly-4445941974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-log-on-software-4442343639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Private Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-private-cloud-engineer-at-terasky-4446116130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-at-shavit-software-4444427268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-exodigo-4444440128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobscroller-4444835562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4444119342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4445935918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4375558561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmeq, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-kla-4433797118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communications-system-engineer-at-iai-israel-aerospace-industries-4443271695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kms-lighthouse-4446064508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
@@ -1149,10 +1152,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6%</t>
+    <t xml:space="preserve">59.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1164,6 +1167,12 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
   </si>
   <si>
@@ -1203,25 +1212,22 @@
     <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSO Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Databases, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-systems-engineer-at-nso-group-4443299999</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
   </si>
   <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
@@ -1233,132 +1239,69 @@
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CertifyOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar-Ilan University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Terraform/IaC, Networking, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-bar-ilan-university-4446564670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives Intralogistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-intralogistics-4446042176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -1371,6 +1314,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
@@ -1383,19 +1341,40 @@
     <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1410,19 +1389,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1574,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -1590,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1598,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1147</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="10">
@@ -1606,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1670,7 +1646,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1678,7 +1654,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1697,36 +1673,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1734,7 +1710,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1756,103 +1732,103 @@
         <v>357</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="B2" s="3">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="B4" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B7" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>365</v>
+        <v>457</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>464</v>
+        <v>251</v>
       </c>
       <c r="B9" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B10" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>466</v>
+        <v>366</v>
       </c>
       <c r="B11" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>359</v>
+        <v>459</v>
       </c>
       <c r="B13" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1860,23 +1836,23 @@
         <v>360</v>
       </c>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>467</v>
+        <v>363</v>
       </c>
       <c r="B15" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1901,13 +1877,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
@@ -1915,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1930,88 +1906,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3">
-        <v>39.2</v>
+        <v>35.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.2</v>
+        <v>38.2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2023,8 +1999,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2095,7 +2071,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -2127,7 +2103,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2159,7 +2135,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -2191,7 +2167,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -2223,7 +2199,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -2255,7 +2231,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
@@ -2287,7 +2263,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -2319,7 +2295,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -2351,7 +2327,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -2383,7 +2359,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -2415,7 +2391,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -2447,7 +2423,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -2479,7 +2455,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2511,7 +2487,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2543,7 +2519,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2551,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -2607,7 +2583,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -2639,7 +2615,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -2671,7 +2647,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -2703,7 +2679,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2735,7 +2711,7 @@
         <v>130</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2767,7 +2743,7 @@
         <v>136</v>
       </c>
       <c r="J23" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
@@ -2784,20 +2760,22 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="J24" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -2805,93 +2783,91 @@
         <v>140</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>144</v>
       </c>
       <c r="J25" s="3">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="J26" s="3">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>150</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>151</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="J27" s="3">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2905,7 +2881,7 @@
         <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2918,7 +2894,7 @@
         <v>154</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -2926,16 +2902,16 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
@@ -2945,10 +2921,10 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2959,13 +2935,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
@@ -2975,27 +2951,27 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="J30" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -3005,10 +2981,10 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="J31" s="3">
         <v>1</v>
@@ -3019,10 +2995,10 @@
         <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
@@ -3035,10 +3011,10 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="J32" s="3">
         <v>2</v>
@@ -3049,10 +3025,10 @@
         <v>116</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3065,27 +3041,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3095,13 +3071,13 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3109,13 +3085,13 @@
         <v>116</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>43</v>
@@ -3125,13 +3101,13 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3139,13 +3115,13 @@
         <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3155,57 +3131,57 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="J36" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>43</v>
@@ -3215,43 +3191,43 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="J38" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -3259,13 +3235,13 @@
         <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3275,24 +3251,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>122</v>
@@ -3305,27 +3281,27 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>43</v>
@@ -3335,13 +3311,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
@@ -3349,13 +3325,13 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>43</v>
@@ -3365,57 +3341,57 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="J43" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>43</v>
@@ -3425,13 +3401,13 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="J45" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3439,10 +3415,10 @@
         <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3455,27 +3431,27 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>43</v>
@@ -3485,54 +3461,54 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J47" s="3">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J48" s="3">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
@@ -3545,27 +3521,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>130</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3581,48 +3557,48 @@
         <v>223</v>
       </c>
       <c r="J50" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3635,54 +3611,54 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="J52" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J53" s="3">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3695,154 +3671,154 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="J54" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="J56" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>53</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="J57" s="3">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>205</v>
+        <v>90</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
@@ -3850,21 +3826,21 @@
         <v>252</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="J59" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>49</v>
@@ -3877,13 +3853,13 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="J60" s="3">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61">
@@ -3894,13 +3870,13 @@
         <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
@@ -3910,10 +3886,10 @@
         <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -3924,37 +3900,37 @@
         <v>261</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>263</v>
+        <v>130</v>
       </c>
       <c r="J62" s="3">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -3967,73 +3943,73 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="J63" s="3">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="J64" s="3">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>272</v>
+        <v>95</v>
       </c>
       <c r="J65" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4041,10 +4017,10 @@
         <v>273</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
@@ -4057,43 +4033,43 @@
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J66" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="J67" s="3">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
@@ -4123,18 +4099,18 @@
         <v>282</v>
       </c>
       <c r="J68" s="3">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
@@ -4147,13 +4123,13 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -4161,13 +4137,13 @@
         <v>286</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="D70" s="3" t="s">
-        <v>289</v>
+        <v>246</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4177,27 +4153,27 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>95</v>
       </c>
       <c r="J70" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>291</v>
+        <v>116</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4207,42 +4183,40 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>296</v>
-      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J72" s="3">
         <v>0</v>
@@ -4250,76 +4224,76 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>116</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="J73" s="3">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="J74" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>303</v>
+        <v>152</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>38</v>
@@ -4329,40 +4303,40 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>53</v>
+        <v>302</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J76" s="3">
         <v>0</v>
@@ -4370,29 +4344,29 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>175</v>
+        <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="J77" s="3">
         <v>2</v>
@@ -4400,16 +4374,16 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>246</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>38</v>
@@ -4419,75 +4393,73 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="J78" s="3">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>116</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>242</v>
-      </c>
+      <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>315</v>
+        <v>53</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4495,13 +4467,13 @@
         <v>315</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>153</v>
+        <v>317</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>49</v>
+        <v>318</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
@@ -4511,13 +4483,13 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>319</v>
+        <v>169</v>
       </c>
       <c r="J81" s="3">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -4544,27 +4516,27 @@
         <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="J82" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="C83" s="3" t="s">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
@@ -4574,27 +4546,27 @@
         <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>326</v>
+        <v>215</v>
       </c>
       <c r="J83" s="3">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>328</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
@@ -4604,24 +4576,24 @@
         <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="J84" s="3">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>158</v>
+        <v>332</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>159</v>
+        <v>333</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>122</v>
+        <v>334</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4631,10 +4603,10 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4645,13 +4617,13 @@
         <v>331</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>43</v>
@@ -4661,24 +4633,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="J86" s="3">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>122</v>
@@ -4691,27 +4663,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>130</v>
+        <v>330</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>287</v>
+        <v>342</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>289</v>
+        <v>122</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4721,24 +4693,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="J88" s="3">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4751,27 +4723,27 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>287</v>
+        <v>185</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>43</v>
@@ -4781,10 +4753,10 @@
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="J90" s="3">
         <v>0</v>
@@ -4792,13 +4764,13 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>122</v>
@@ -4811,24 +4783,24 @@
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>122</v>
@@ -4841,77 +4813,17 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>130</v>
+        <v>356</v>
       </c>
       <c r="J92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J93" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J92"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5004,8 +4916,6 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5013,9 +4923,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5047,32 +4957,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5080,7 +4990,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4">
@@ -5088,10 +4998,10 @@
         <v>116</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5099,18 +5009,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>116</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5118,18 +5028,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5137,18 +5047,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5156,18 +5066,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5175,18 +5085,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5194,18 +5104,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>257</v>
+        <v>116</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5213,18 +5123,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>295</v>
+        <v>207</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5232,18 +5142,18 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5251,18 +5161,18 @@
         <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>313</v>
+        <v>192</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5270,18 +5180,18 @@
         <v>23</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5289,18 +5199,18 @@
         <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5308,18 +5218,18 @@
         <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>342</v>
+        <v>174</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5327,7 +5237,7 @@
         <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17">
@@ -5335,10 +5245,10 @@
         <v>347</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -5346,18 +5256,18 @@
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>174</v>
+        <v>352</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5365,7 +5275,7 @@
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -5417,23 +5327,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>242</v>
+        <v>360</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -5441,7 +5351,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B6" s="3">
         <v>11</v>
@@ -5449,7 +5359,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
@@ -5457,15 +5367,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -5473,15 +5383,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5489,7 +5399,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5497,7 +5407,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5505,7 +5415,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5513,7 +5423,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5521,7 +5431,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5534,7 +5444,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5543,7 +5453,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -5564,47 +5474,47 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>215</v>
+        <v>132</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5612,7 +5522,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5620,7 +5530,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5628,7 +5538,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5636,7 +5546,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5644,7 +5554,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5652,7 +5562,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5660,10 +5570,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5674,23 +5584,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -5740,13 +5650,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
-        <v>8.8</v>
+        <v>6.2</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5754,10 +5664,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5768,13 +5678,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="C7" s="3">
-        <v>5.6</v>
+        <v>5.0</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5782,13 +5692,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="C8" s="3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5796,13 +5706,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5810,13 +5720,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5824,13 +5734,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5838,13 +5748,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5852,13 +5762,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C13" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5866,7 +5776,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -5880,7 +5790,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5894,7 +5804,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5920,10 +5830,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5931,7 +5841,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5942,10 +5852,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4">
@@ -5953,10 +5863,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -5975,7 +5885,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
@@ -5983,7 +5893,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -5991,20 +5901,20 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>246</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6012,7 +5922,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6020,17 +5930,25 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>289</v>
+        <v>112</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6043,7 +5961,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6055,10 +5973,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -6070,10 +5988,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6090,31 +6008,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>381</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>267</v>
+        <v>127</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>383</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>385</v>
+        <v>129</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>217</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
@@ -6122,31 +6040,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>391</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
@@ -6154,31 +6072,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>247</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5">
@@ -6186,31 +6104,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>184</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -6218,31 +6136,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>399</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="F6" s="3">
-        <v>92</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
@@ -6250,31 +6168,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F7" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6282,31 +6200,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>404</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="F8" s="3">
+        <v>83</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="F8" s="3">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>407</v>
+        <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>408</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -6314,31 +6232,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F9" s="3">
         <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -6346,31 +6264,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>415</v>
+        <v>271</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F10" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>164</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11">
@@ -6378,31 +6296,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>333</v>
+        <v>395</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>348</v>
+        <v>415</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>349</v>
+        <v>174</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F11" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>420</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
@@ -6410,31 +6328,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="F12" s="3">
-        <v>74</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>223</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -6442,31 +6360,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>426</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>423</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="F13" s="3">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>424</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>164</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14">
@@ -6474,31 +6392,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F14" s="3">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F14" s="3">
-        <v>74</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>431</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>432</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -6506,31 +6424,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="F15" s="3">
+        <v>52</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="F15" s="3">
-        <v>70</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="16">
@@ -6538,22 +6456,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F16" s="3">
+        <v>52</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="F16" s="3">
-        <v>70</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>434</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
@@ -6570,31 +6488,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F17" s="3">
-        <v>68</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -6602,31 +6520,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>443</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F18" s="3">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>445</v>
+        <v>62</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>408</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -6634,31 +6552,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>447</v>
+        <v>229</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F19" s="3">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20">
@@ -6666,31 +6584,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="F20" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>453</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21">
@@ -6698,31 +6616,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="F21" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>458</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W31.xlsx
+++ b/reports/devops-jobs-israel-2026-W31.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-31T09:13:07</t>
+    <t xml:space="preserve">2026-08-02T08:34:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">2.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
@@ -399,897 +399,1023 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445035673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-engineer-at-tipuli-tech-4447115888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-aws-at-ur-tech-jobs-4447639616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-abra-4447643479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantis Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-mantis-tech-4445820865</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Operations Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Axonius</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-operations-engineer-at-axonius-4444135962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cato-networks-4430441382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThetaRay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playtika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-playtika-4417616851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Specialist - 20705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-20705-at-comblack-4447008409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zadara-4381499747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-position-at-lab42-4445607255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Fend Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4445937741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4410866558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-at-teads-4436613100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streaming Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIDAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-platform-engineer-at-vidaa-4444520220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ata, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4437329124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Security - AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-security-ai-platform-engineer-at-cato-networks-4416844175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Lead - DevOps And Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-lead-devops-and-cloud-at-terasky-4446108207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer – Test Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4444119342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-abra-4446717885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-snke-4445005467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-at-elbit-systems-israel-4375575135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orca AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-orca-ai-4444111655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4427766128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobScroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobscroller-4444835562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Storage &amp; Backup Infrastructure Engineer (5489)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-storage-backup-infrastructure-engineer-5489-at-ingima-4447886277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Satellite System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsatellite-system-engineer-at-jobsseek-4445198084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (36620 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Reliability Engineer MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratacom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Automation Engineer - Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-automation-engineer-networking-at-cato-networks-4378169465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4446049070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Talent Acquisition Partner - R&amp;D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8576517002&amp;gh_jid=8576517002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering Manager, AI Platform Enablement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/melio/jobs/7747499003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiliot-4446820849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4445035673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-datateam-4445010424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; Automation Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-automation-engineer-at-abra-4446717885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-akeyless-security-4445763841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlueBird Aero Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-bluebird-aero-systems-ltd-4441546017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4442333778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4445937741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sela-4443226746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D-Fend Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-d-fend-solutions-4447057704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABdevops-engineer-at-jobsseek-4445184888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist - 20705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-20705-at-comblack-4447008409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-wiz-4406742504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThetaRay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-thetaray-4446919831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-zenity-4443820290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-checkmarx-4446765835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps / Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-site-reliability-engineer-sre-at-lendbuzz-4437323317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-position-at-lab42-4445607255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-elbit-systems-israel-4384496448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader - Infra and DevEx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-infra-and-devex-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-skai-4427485314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4437791495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tools &amp; Automation Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integra LifeSciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tools-automation-specialist-at-integra-lifesciences-4377406238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4444102865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior HPC Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-site-reliability-engineer-at-nvidia-4395468649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-cortex-at-palo-alto-networks-4398688765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Reliability Engineer MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratacom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-reliability-engineer-mi-at-stratacom-4446130177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-engineer-at-gong-4428620466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-maytronics-4437388572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4442813126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer – Test Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-%E2%80%93-test-environments-at-comblack-4446757352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-4434371817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-nvidia-4427778531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-platform-engineer-at-nvidia-ai-4443239045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streaming Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIDAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/streaming-platform-engineer-at-vidaa-4444520220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4446179787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-arad-technologies-4445126362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-log-on-software-4442343639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps/IT Enginee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-it-enginee-at-ngsoft-4443682298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4444119342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-at-nebius-4437660618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-snke-4445005467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Infrastructure Engineer (Modiin)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-infrastructure-engineer-modiin-at-nebius-4437655743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Cloud Infrastructure Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobScroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobscroller-4444835562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (36620 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-36620-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4446723677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Satellite System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsatellite-system-engineer-at-jobsseek-4445198084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Istra Research Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-istra-research-ltd-4445368227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-cloud-infrastructure-engineering-at-jobgether-4444337826</t>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CertifyOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Terraform/IaC, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-dialog-4442351473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -1314,21 +1440,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
   </si>
   <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
   </si>
   <si>
@@ -1338,43 +1449,34 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4442335619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1386,19 +1488,22 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1550,7 +1655,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1558,7 +1663,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1566,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
@@ -1574,7 +1679,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1164</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="10">
@@ -1582,7 +1687,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1646,7 +1751,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -1654,7 +1759,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1673,36 +1778,36 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="B2" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1710,7 +1815,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1729,130 +1834,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>364</v>
+        <v>489</v>
       </c>
       <c r="B5" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>455</v>
+        <v>490</v>
       </c>
       <c r="B6" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>456</v>
+        <v>260</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>494</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>363</v>
+        <v>164</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1877,13 +1982,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>462</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2">
@@ -1891,13 +1996,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1906,88 +2011,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3">
-        <v>35.5</v>
+        <v>32.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>465</v>
+        <v>500</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>466</v>
+        <v>501</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>38.2</v>
+        <v>29.7</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.5</v>
+        <v>14.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.1</v>
+        <v>15.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2071,7 +2176,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -2103,7 +2208,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2135,7 +2240,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -2167,7 +2272,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -2199,7 +2304,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -2231,7 +2336,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -2263,7 +2368,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -2295,7 +2400,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -2327,7 +2432,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="3">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -2359,7 +2464,7 @@
         <v>73</v>
       </c>
       <c r="J11" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2391,7 +2496,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
@@ -2423,7 +2528,7 @@
         <v>90</v>
       </c>
       <c r="J13" s="3">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -2455,7 +2560,7 @@
         <v>95</v>
       </c>
       <c r="J14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2487,7 +2592,7 @@
         <v>46</v>
       </c>
       <c r="J15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2519,7 +2624,7 @@
         <v>102</v>
       </c>
       <c r="J16" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2656,7 @@
         <v>77</v>
       </c>
       <c r="J17" s="3">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -2583,7 +2688,7 @@
         <v>109</v>
       </c>
       <c r="J18" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -2615,7 +2720,7 @@
         <v>115</v>
       </c>
       <c r="J19" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -2647,7 +2752,7 @@
         <v>41</v>
       </c>
       <c r="J20" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
@@ -2679,7 +2784,7 @@
         <v>125</v>
       </c>
       <c r="J21" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -2690,7 +2795,7 @@
         <v>127</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>49</v>
@@ -2699,30 +2804,30 @@
         <v>38</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J22" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>49</v>
@@ -2731,51 +2836,49 @@
         <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="J23" s="3">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>138</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J24" s="3">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -2786,15 +2889,17 @@
         <v>141</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
@@ -2802,42 +2907,40 @@
         <v>143</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="J25" s="3">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J26" s="3">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2845,10 +2948,10 @@
         <v>116</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2861,27 +2964,27 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J27" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>43</v>
@@ -2891,10 +2994,10 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -2902,7 +3005,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>157</v>
@@ -2924,54 +3027,56 @@
         <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>43</v>
@@ -2981,43 +3086,43 @@
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3028,7 +3133,7 @@
         <v>170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3041,27 +3146,27 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="J33" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>43</v>
@@ -3074,10 +3179,10 @@
         <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>46</v>
+        <v>156</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3088,7 +3193,7 @@
         <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
@@ -3104,24 +3209,24 @@
         <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="J35" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3131,87 +3236,87 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
@@ -3221,13 +3326,13 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="J39" s="3">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
@@ -3235,10 +3340,10 @@
         <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
@@ -3251,24 +3356,24 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="J40" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>122</v>
@@ -3281,13 +3386,13 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -3295,10 +3400,10 @@
         <v>116</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3311,13 +3416,13 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -3325,10 +3430,10 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>122</v>
@@ -3341,24 +3446,24 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3371,54 +3476,54 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>116</v>
+        <v>211</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3426,89 +3531,91 @@
       <c r="E46" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G46" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J47" s="3">
-        <v>67</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>215</v>
+        <v>147</v>
       </c>
       <c r="J48" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
@@ -3521,27 +3628,27 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>130</v>
+        <v>224</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3551,27 +3658,27 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="J50" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3581,27 +3688,27 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>43</v>
@@ -3611,24 +3718,24 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>49</v>
@@ -3641,24 +3748,24 @@
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="J53" s="3">
-        <v>70</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
@@ -3671,24 +3778,24 @@
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="J54" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
@@ -3701,27 +3808,27 @@
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>115</v>
       </c>
       <c r="J55" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>60</v>
+        <v>246</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>43</v>
@@ -3731,146 +3838,146 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="J56" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="J57" s="3">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>245</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>246</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="J58" s="3">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>251</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="J60" s="3">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
@@ -3883,54 +3990,54 @@
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="J61" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>262</v>
+        <v>149</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
@@ -3943,207 +4050,207 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="J63" s="3">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>172</v>
+        <v>95</v>
       </c>
       <c r="J64" s="3">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="J66" s="3">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>49</v>
+        <v>284</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="J67" s="3">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>144</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>122</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="J68" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>285</v>
+        <v>46</v>
       </c>
       <c r="J69" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>246</v>
+        <v>49</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>43</v>
@@ -4153,13 +4260,13 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="J70" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4167,13 +4274,13 @@
         <v>116</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>43</v>
@@ -4183,24 +4290,24 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
       <c r="J71" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>192</v>
+        <v>297</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>174</v>
+        <v>298</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>122</v>
@@ -4213,24 +4320,24 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>293</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>122</v>
@@ -4243,27 +4350,27 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>296</v>
+        <v>160</v>
       </c>
       <c r="J73" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>43</v>
@@ -4273,24 +4380,24 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>299</v>
+        <v>156</v>
       </c>
       <c r="J74" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>152</v>
+        <v>277</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>122</v>
@@ -4303,24 +4410,24 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>95</v>
+        <v>305</v>
       </c>
       <c r="J75" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>303</v>
+        <v>201</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>49</v>
@@ -4328,32 +4435,34 @@
       <c r="E76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>155</v>
+        <v>308</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>150</v>
+        <v>311</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>43</v>
@@ -4363,144 +4472,144 @@
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>169</v>
+        <v>313</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>307</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>309</v>
+        <v>149</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>246</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="J78" s="3">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>116</v>
+        <v>316</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>122</v>
+        <v>231</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>53</v>
+        <v>319</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>313</v>
+        <v>219</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>317</v>
+        <v>149</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>318</v>
+        <v>49</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="J81" s="3">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>122</v>
@@ -4513,54 +4622,54 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>161</v>
+        <v>329</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>215</v>
+        <v>151</v>
       </c>
       <c r="J83" s="3">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>122</v>
@@ -4573,27 +4682,27 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>330</v>
+        <v>233</v>
       </c>
       <c r="J84" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>43</v>
@@ -4603,24 +4712,24 @@
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>49</v>
@@ -4633,24 +4742,24 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J86" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>122</v>
@@ -4663,24 +4772,24 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>330</v>
+        <v>233</v>
       </c>
       <c r="J87" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>122</v>
@@ -4693,24 +4802,24 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>122</v>
@@ -4723,70 +4832,70 @@
         <v>23</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>155</v>
+        <v>350</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>348</v>
+        <v>154</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>352</v>
+        <v>149</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4794,13 +4903,13 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>354</v>
+        <v>297</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>122</v>
@@ -4813,17 +4922,289 @@
         <v>23</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>356</v>
+        <v>217</v>
       </c>
       <c r="J92" s="3">
-        <v>5</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J93" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J95" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J96" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J97" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J98" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J99" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J100" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J101" s="3">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J101"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4916,6 +5297,15 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4923,8 +5313,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -4957,13 +5347,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4971,18 +5361,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4990,18 +5380,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5009,18 +5399,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5028,18 +5418,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5047,7 +5437,7 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -5055,10 +5445,10 @@
         <v>116</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>199</v>
+        <v>302</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5066,18 +5456,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>316</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>202</v>
+        <v>317</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5085,18 +5475,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>203</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>204</v>
+        <v>353</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>354</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5104,18 +5494,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>206</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>116</v>
+        <v>361</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>207</v>
+        <v>362</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5123,163 +5513,11 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5290,14 +5528,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5311,23 +5541,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="B3" s="3">
         <v>14</v>
@@ -5335,15 +5565,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>361</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -5351,39 +5581,39 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -5391,7 +5621,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>147</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -5399,7 +5629,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -5407,7 +5637,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>368</v>
+        <v>142</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -5415,7 +5645,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -5423,7 +5653,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5431,7 +5661,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -5444,7 +5674,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5453,7 +5683,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5474,15 +5704,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>277</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>254</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5490,23 +5720,23 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>297</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5514,7 +5744,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5522,7 +5752,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5530,7 +5760,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5538,7 +5768,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5546,7 +5776,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5554,7 +5784,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5562,7 +5792,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5570,7 +5800,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5584,23 +5814,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
@@ -5664,13 +5894,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>277</v>
       </c>
       <c r="C6" s="3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5678,10 +5908,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5692,13 +5922,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>254</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3">
-        <v>4.2</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5706,13 +5936,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3">
-        <v>2.9</v>
+        <v>5.0</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5720,13 +5950,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>152</v>
+        <v>297</v>
       </c>
       <c r="C10" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -5734,13 +5964,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="C11" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5748,13 +5978,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5762,10 +5992,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5776,10 +6006,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5790,7 +6020,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5804,7 +6034,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5830,10 +6060,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
@@ -5841,7 +6071,7 @@
         <v>92</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -5852,10 +6082,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
@@ -5863,10 +6093,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5885,7 +6115,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2">
@@ -5893,7 +6123,7 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -5901,7 +6131,7 @@
         <v>122</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -5914,7 +6144,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5922,31 +6152,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5973,10 +6203,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5988,10 +6218,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -6008,31 +6238,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>87</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>129</v>
+        <v>410</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
@@ -6040,31 +6270,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>274</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>211</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -6072,31 +6302,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5">
@@ -6104,31 +6334,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6">
@@ -6136,31 +6366,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
@@ -6168,31 +6398,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>335</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>86</v>
+        <v>338</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>94</v>
+        <v>339</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -6200,31 +6430,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -6232,31 +6462,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>407</v>
+        <v>219</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>403</v>
-      </c>
       <c r="F9" s="3">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>410</v>
+        <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -6264,31 +6494,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>412</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>271</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>414</v>
+        <v>45</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>330</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -6296,31 +6526,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>174</v>
+        <v>438</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="F11" s="3">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>440</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>356</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -6328,31 +6558,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13">
@@ -6360,31 +6590,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>447</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>448</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>426</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -6392,31 +6622,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>391</v>
+        <v>453</v>
       </c>
       <c r="F14" s="3">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>84</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15">
@@ -6424,31 +6654,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>403</v>
-      </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16">
@@ -6456,31 +6686,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>461</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17">
@@ -6488,31 +6718,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>84</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18">
@@ -6520,31 +6750,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>469</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>470</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -6552,31 +6782,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20">
@@ -6584,31 +6814,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>271</v>
+        <v>477</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>356</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21">
@@ -6616,31 +6846,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>150</v>
+        <v>482</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>282</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
